--- a/LUXAS株式会社/必要資料一覧_LUXAS株式会社_20260923.xlsx
+++ b/LUXAS株式会社/必要資料一覧_LUXAS株式会社_20260923.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$B$1:$F$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$B$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -218,7 +218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,21 +359,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -752,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" style="1" min="1" max="1"/>
@@ -811,100 +796,88 @@
       <c r="F3" s="16" t="n"/>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="39">
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="34" t="n"/>
+      <c r="D4" s="34">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>株主名簿（株主名・持株数・持株比率がわかるもの）</t>
         </is>
       </c>
-      <c r="F4" s="29" t="n"/>
-    </row>
-    <row r="5" ht="20.5" customHeight="1" s="39" thickBot="1">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="F4" s="28" t="n"/>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="39" thickBot="1">
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>駐車場用地（89.4㎡）の固定資産税課税明細書または不動産登記簿謄本　※土地の時価評価に使用します</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="n"/>
+    </row>
+    <row r="6" ht="20.5" customHeight="1" s="39" thickTop="1">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D5" s="45">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="D6" s="45">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E6" s="46" t="inlineStr">
         <is>
           <t>決算書・勘定科目内訳明細書・法人税／消費税申告書（直近3期分）</t>
         </is>
       </c>
-      <c r="F5" s="47" t="inlineStr">
+      <c r="F6" s="47" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20.5" customHeight="1" s="39" thickTop="1">
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E6" s="38" t="inlineStr">
+    <row r="7" ht="20.5" customHeight="1" s="39">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>月次試算表（2026年7月分以降）　※2026年6月分までは受領済</t>
         </is>
       </c>
-      <c r="F6" s="9" t="n"/>
-    </row>
-    <row r="7" ht="20.5" customHeight="1" s="39">
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="20.5" customHeight="1" s="39">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>借入金の返済予定表（金融機関別・直近のもの）</t>
         </is>
       </c>
-      <c r="F7" s="10" t="n"/>
-    </row>
-    <row r="8" ht="30.75" customHeight="1" s="39">
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>Ⅲ</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>事業</t>
-        </is>
-      </c>
-      <c r="D8" s="45">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E8" s="46" t="inlineStr">
-        <is>
-          <t>店舗別の売上・粗利がわかる資料（2025年12月〜2026年6月）</t>
-        </is>
-      </c>
-      <c r="F8" s="47" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20.5" customHeight="1" s="39">
+      <c r="F8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="30.75" customHeight="1" s="39">
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="34" t="n"/>
       <c r="D9" s="34">
@@ -913,129 +886,219 @@
       </c>
       <c r="E9" s="38" t="inlineStr">
         <is>
+          <t>減価償却資産台帳（2025年11月期末時点）　※償却の過不足額の確認に使用します</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="30.75" customHeight="1" s="39" thickBot="1">
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>差入保証金（27,371千円）・長期前払費用（1,712千円）の内訳がわかる資料</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="20.5" customHeight="1" s="39" thickTop="1">
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Ⅲ</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="D11" s="45">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>店舗別の売上・粗利がわかる資料（2025年12月〜2026年6月）</t>
+        </is>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30.75" customHeight="1" s="39">
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
           <t>撤退2店舗（アクアウォーク大垣店・ペットプラザ岐阜店）の原状回復費用・違約金がわかる資料</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="30.75" customHeight="1" s="39" thickBot="1">
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="45" t="n"/>
-      <c r="D10" s="45">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="30.75" customHeight="1" s="39">
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="45" t="n"/>
+      <c r="D13" s="45">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E13" s="46" t="inlineStr">
         <is>
           <t>棚卸資産の内訳（2025年11月期末）　※2026年3月計上の廃棄損44,000千円の処分方法・証憑もあわせてご教示ください</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F13" s="47" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.75" customHeight="1" s="39" thickTop="1">
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+    <row r="14" ht="20.5" customHeight="1" s="39">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>ペット保険の代理店手数料がわかる資料（直近1期分の精算書等）</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" s="39">
-      <c r="B12" s="44" t="inlineStr">
-        <is>
-          <t>Ⅳ</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>人事</t>
-        </is>
-      </c>
-      <c r="D12" s="48">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E12" s="46" t="inlineStr">
-        <is>
-          <t>従業員名簿（氏名・生年月日・入社年月日・雇用形態・勤務店舗がわかるもの）</t>
-        </is>
-      </c>
-      <c r="F12" s="47" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21.75" customHeight="1" s="39">
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="50" t="n"/>
-      <c r="D13" s="51">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E13" s="52" t="inlineStr">
-        <is>
-          <t>給与台帳（直近1期分｜直近の年末調整の資料等）</t>
-        </is>
-      </c>
-      <c r="F13" s="53" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20.5" customHeight="1" s="39">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Ⅴ</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>契約</t>
-        </is>
-      </c>
-      <c r="D14" s="34">
-        <f>ROW()-2</f>
-        <v/>
-      </c>
-      <c r="E14" s="38" t="inlineStr">
-        <is>
-          <t>フランチャイズ契約書（有限会社ワンラブ）</t>
-        </is>
-      </c>
       <c r="F14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30.75" customHeight="1" s="39" thickBot="1">
+    <row r="15" ht="20.5" customHeight="1" s="39" thickBot="1">
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="7">
+      <c r="D15" s="3">
         <f>ROW()-2</f>
         <v/>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>店舗の賃貸借契約書（稼働6店舗分。FC本部からの転借契約を含む）</t>
+          <t>事業用車両3台の車検証または査定書　※車両運搬具の時価評価に使用します</t>
         </is>
       </c>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="20.5" customHeight="1" s="39" thickTop="1"/>
-    <row r="17" ht="20.5" customHeight="1" s="39"/>
-    <row r="18" ht="20.5" customHeight="1" s="39"/>
-    <row r="19" ht="20.5" customHeight="1" s="39" thickBot="1"/>
-    <row r="20" ht="20.5" customHeight="1" s="39" thickTop="1"/>
-    <row r="21" ht="20.5" customHeight="1" s="39" thickBot="1"/>
+    <row r="16" ht="20.5" customHeight="1" s="39" thickTop="1">
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>Ⅳ</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>人事</t>
+        </is>
+      </c>
+      <c r="D16" s="48">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E16" s="46" t="inlineStr">
+        <is>
+          <t>従業員名簿（氏名・生年月日・入社年月日・雇用形態・勤務店舗がわかるもの）</t>
+        </is>
+      </c>
+      <c r="F16" s="47" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20.5" customHeight="1" s="39">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="48">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>給与台帳（直近1期分｜直近の年末調整の資料等）</t>
+        </is>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20.5" customHeight="1" s="39">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="37">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>退職金規程・役員退職慰労金規程　※制度がない場合はその旨をご教示ください</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="30.75" customHeight="1" s="39" thickBot="1">
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="7">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>賞与の支給実績・支給対象期間がわかる資料　※制度がない場合はその旨をご教示ください</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="20.5" customHeight="1" s="39" thickTop="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Ⅴ</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>契約</t>
+        </is>
+      </c>
+      <c r="D20" s="34">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>フランチャイズ契約書（有限会社ワンラブ）</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="30.75" customHeight="1" s="39" thickBot="1">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="7">
+        <f>ROW()-2</f>
+        <v/>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>店舗の賃貸借契約書（稼働6店舗分。FC本部からの転借契約を含む）　※敷金の償却条項・返還条件の確認に使用します</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="n"/>
+    </row>
     <row r="22" ht="13.5" customHeight="1" s="39" thickTop="1"/>
   </sheetData>
   <mergeCells count="2">
